--- a/Estandar/Curvas.xlsx
+++ b/Estandar/Curvas.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="17412" windowHeight="13056" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curvas Concreto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,8 +25,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -40,14 +40,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-        <bgColor rgb="00E7E6E6"/>
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,8 +82,52 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <extend val="0"/>
+        <sz val="11"/>
+        <vertAlign val="baseline"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4472C4"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -154,6 +198,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:F913" headerRowCount="1" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F913"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Tipo de Concreto" dataDxfId="5"/>
+    <tableColumn id="2" name="Tipo Elemento" dataDxfId="4"/>
+    <tableColumn id="3" name="Resistencia Diseño (MPa)" dataDxfId="3"/>
+    <tableColumn id="4" name="Día" dataDxfId="2"/>
+    <tableColumn id="5" name="Llave" dataDxfId="1"/>
+    <tableColumn id="6" name="Resistencia Teórica (MPa)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,14 +505,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F913"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23.88671875" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24.33203125" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21244,7 +21303,7 @@
       </c>
       <c r="B800" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C800" s="3" t="n">
@@ -21255,7 +21314,7 @@
       </c>
       <c r="E800" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-0</t>
+          <t>TREMIE-21-0</t>
         </is>
       </c>
       <c r="F800" s="3" t="n">
@@ -21270,7 +21329,7 @@
       </c>
       <c r="B801" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C801" s="5" t="n">
@@ -21281,7 +21340,7 @@
       </c>
       <c r="E801" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-1</t>
+          <t>TREMIE-21-1</t>
         </is>
       </c>
       <c r="F801" s="5" t="n">
@@ -21296,7 +21355,7 @@
       </c>
       <c r="B802" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C802" s="3" t="n">
@@ -21307,7 +21366,7 @@
       </c>
       <c r="E802" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-2</t>
+          <t>TREMIE-21-2</t>
         </is>
       </c>
       <c r="F802" s="3" t="n">
@@ -21322,7 +21381,7 @@
       </c>
       <c r="B803" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C803" s="5" t="n">
@@ -21333,7 +21392,7 @@
       </c>
       <c r="E803" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-3</t>
+          <t>TREMIE-21-3</t>
         </is>
       </c>
       <c r="F803" s="5" t="n">
@@ -21348,7 +21407,7 @@
       </c>
       <c r="B804" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C804" s="3" t="n">
@@ -21359,7 +21418,7 @@
       </c>
       <c r="E804" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-4</t>
+          <t>TREMIE-21-4</t>
         </is>
       </c>
       <c r="F804" s="3" t="n">
@@ -21374,7 +21433,7 @@
       </c>
       <c r="B805" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C805" s="5" t="n">
@@ -21385,7 +21444,7 @@
       </c>
       <c r="E805" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-5</t>
+          <t>TREMIE-21-5</t>
         </is>
       </c>
       <c r="F805" s="5" t="n">
@@ -21400,7 +21459,7 @@
       </c>
       <c r="B806" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C806" s="3" t="n">
@@ -21411,7 +21470,7 @@
       </c>
       <c r="E806" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-6</t>
+          <t>TREMIE-21-6</t>
         </is>
       </c>
       <c r="F806" s="3" t="n">
@@ -21426,7 +21485,7 @@
       </c>
       <c r="B807" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C807" s="5" t="n">
@@ -21437,7 +21496,7 @@
       </c>
       <c r="E807" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-7</t>
+          <t>TREMIE-21-7</t>
         </is>
       </c>
       <c r="F807" s="5" t="n">
@@ -21452,7 +21511,7 @@
       </c>
       <c r="B808" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C808" s="3" t="n">
@@ -21463,7 +21522,7 @@
       </c>
       <c r="E808" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-8</t>
+          <t>TREMIE-21-8</t>
         </is>
       </c>
       <c r="F808" s="3" t="n">
@@ -21478,7 +21537,7 @@
       </c>
       <c r="B809" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C809" s="5" t="n">
@@ -21489,7 +21548,7 @@
       </c>
       <c r="E809" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-9</t>
+          <t>TREMIE-21-9</t>
         </is>
       </c>
       <c r="F809" s="5" t="n">
@@ -21504,7 +21563,7 @@
       </c>
       <c r="B810" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C810" s="3" t="n">
@@ -21515,7 +21574,7 @@
       </c>
       <c r="E810" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-10</t>
+          <t>TREMIE-21-10</t>
         </is>
       </c>
       <c r="F810" s="3" t="n">
@@ -21530,7 +21589,7 @@
       </c>
       <c r="B811" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C811" s="5" t="n">
@@ -21541,7 +21600,7 @@
       </c>
       <c r="E811" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-11</t>
+          <t>TREMIE-21-11</t>
         </is>
       </c>
       <c r="F811" s="5" t="n">
@@ -21556,7 +21615,7 @@
       </c>
       <c r="B812" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C812" s="3" t="n">
@@ -21567,7 +21626,7 @@
       </c>
       <c r="E812" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-12</t>
+          <t>TREMIE-21-12</t>
         </is>
       </c>
       <c r="F812" s="3" t="n">
@@ -21582,7 +21641,7 @@
       </c>
       <c r="B813" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C813" s="5" t="n">
@@ -21593,7 +21652,7 @@
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-13</t>
+          <t>TREMIE-21-13</t>
         </is>
       </c>
       <c r="F813" s="5" t="n">
@@ -21608,7 +21667,7 @@
       </c>
       <c r="B814" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C814" s="3" t="n">
@@ -21619,7 +21678,7 @@
       </c>
       <c r="E814" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-14</t>
+          <t>TREMIE-21-14</t>
         </is>
       </c>
       <c r="F814" s="3" t="n">
@@ -21634,7 +21693,7 @@
       </c>
       <c r="B815" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C815" s="5" t="n">
@@ -21645,7 +21704,7 @@
       </c>
       <c r="E815" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-15</t>
+          <t>TREMIE-21-15</t>
         </is>
       </c>
       <c r="F815" s="5" t="n">
@@ -21660,7 +21719,7 @@
       </c>
       <c r="B816" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C816" s="3" t="n">
@@ -21671,7 +21730,7 @@
       </c>
       <c r="E816" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-16</t>
+          <t>TREMIE-21-16</t>
         </is>
       </c>
       <c r="F816" s="3" t="n">
@@ -21686,7 +21745,7 @@
       </c>
       <c r="B817" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C817" s="5" t="n">
@@ -21697,7 +21756,7 @@
       </c>
       <c r="E817" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-17</t>
+          <t>TREMIE-21-17</t>
         </is>
       </c>
       <c r="F817" s="5" t="n">
@@ -21712,7 +21771,7 @@
       </c>
       <c r="B818" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C818" s="3" t="n">
@@ -21723,7 +21782,7 @@
       </c>
       <c r="E818" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-18</t>
+          <t>TREMIE-21-18</t>
         </is>
       </c>
       <c r="F818" s="3" t="n">
@@ -21738,7 +21797,7 @@
       </c>
       <c r="B819" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C819" s="5" t="n">
@@ -21749,7 +21808,7 @@
       </c>
       <c r="E819" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-19</t>
+          <t>TREMIE-21-19</t>
         </is>
       </c>
       <c r="F819" s="5" t="n">
@@ -21764,7 +21823,7 @@
       </c>
       <c r="B820" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C820" s="3" t="n">
@@ -21775,7 +21834,7 @@
       </c>
       <c r="E820" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-20</t>
+          <t>TREMIE-21-20</t>
         </is>
       </c>
       <c r="F820" s="3" t="n">
@@ -21790,7 +21849,7 @@
       </c>
       <c r="B821" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C821" s="5" t="n">
@@ -21801,7 +21860,7 @@
       </c>
       <c r="E821" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-21</t>
+          <t>TREMIE-21-21</t>
         </is>
       </c>
       <c r="F821" s="5" t="n">
@@ -21816,7 +21875,7 @@
       </c>
       <c r="B822" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C822" s="3" t="n">
@@ -21827,7 +21886,7 @@
       </c>
       <c r="E822" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-22</t>
+          <t>TREMIE-21-22</t>
         </is>
       </c>
       <c r="F822" s="3" t="n">
@@ -21842,7 +21901,7 @@
       </c>
       <c r="B823" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C823" s="5" t="n">
@@ -21853,7 +21912,7 @@
       </c>
       <c r="E823" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-23</t>
+          <t>TREMIE-21-23</t>
         </is>
       </c>
       <c r="F823" s="5" t="n">
@@ -21868,7 +21927,7 @@
       </c>
       <c r="B824" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C824" s="3" t="n">
@@ -21879,7 +21938,7 @@
       </c>
       <c r="E824" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-24</t>
+          <t>TREMIE-21-24</t>
         </is>
       </c>
       <c r="F824" s="3" t="n">
@@ -21894,7 +21953,7 @@
       </c>
       <c r="B825" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C825" s="5" t="n">
@@ -21905,7 +21964,7 @@
       </c>
       <c r="E825" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-25</t>
+          <t>TREMIE-21-25</t>
         </is>
       </c>
       <c r="F825" s="5" t="n">
@@ -21920,7 +21979,7 @@
       </c>
       <c r="B826" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C826" s="3" t="n">
@@ -21931,7 +21990,7 @@
       </c>
       <c r="E826" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-26</t>
+          <t>TREMIE-21-26</t>
         </is>
       </c>
       <c r="F826" s="3" t="n">
@@ -21946,7 +22005,7 @@
       </c>
       <c r="B827" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C827" s="5" t="n">
@@ -21957,7 +22016,7 @@
       </c>
       <c r="E827" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-27</t>
+          <t>TREMIE-21-27</t>
         </is>
       </c>
       <c r="F827" s="5" t="n">
@@ -21972,7 +22031,7 @@
       </c>
       <c r="B828" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C828" s="3" t="n">
@@ -21983,7 +22042,7 @@
       </c>
       <c r="E828" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-28</t>
+          <t>TREMIE-21-28</t>
         </is>
       </c>
       <c r="F828" s="3" t="n">
@@ -21998,7 +22057,7 @@
       </c>
       <c r="B829" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C829" s="5" t="n">
@@ -22009,7 +22068,7 @@
       </c>
       <c r="E829" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-29</t>
+          <t>TREMIE-21-29</t>
         </is>
       </c>
       <c r="F829" s="5" t="n">
@@ -22024,7 +22083,7 @@
       </c>
       <c r="B830" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C830" s="3" t="n">
@@ -22035,7 +22094,7 @@
       </c>
       <c r="E830" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-30</t>
+          <t>TREMIE-21-30</t>
         </is>
       </c>
       <c r="F830" s="3" t="n">
@@ -22050,7 +22109,7 @@
       </c>
       <c r="B831" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C831" s="5" t="n">
@@ -22061,7 +22120,7 @@
       </c>
       <c r="E831" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-31</t>
+          <t>TREMIE-21-31</t>
         </is>
       </c>
       <c r="F831" s="5" t="n">
@@ -22076,7 +22135,7 @@
       </c>
       <c r="B832" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C832" s="3" t="n">
@@ -22087,7 +22146,7 @@
       </c>
       <c r="E832" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-32</t>
+          <t>TREMIE-21-32</t>
         </is>
       </c>
       <c r="F832" s="3" t="n">
@@ -22102,7 +22161,7 @@
       </c>
       <c r="B833" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C833" s="5" t="n">
@@ -22113,7 +22172,7 @@
       </c>
       <c r="E833" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-33</t>
+          <t>TREMIE-21-33</t>
         </is>
       </c>
       <c r="F833" s="5" t="n">
@@ -22128,7 +22187,7 @@
       </c>
       <c r="B834" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C834" s="3" t="n">
@@ -22139,7 +22198,7 @@
       </c>
       <c r="E834" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-34</t>
+          <t>TREMIE-21-34</t>
         </is>
       </c>
       <c r="F834" s="3" t="n">
@@ -22154,7 +22213,7 @@
       </c>
       <c r="B835" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C835" s="5" t="n">
@@ -22165,7 +22224,7 @@
       </c>
       <c r="E835" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-35</t>
+          <t>TREMIE-21-35</t>
         </is>
       </c>
       <c r="F835" s="5" t="n">
@@ -22180,7 +22239,7 @@
       </c>
       <c r="B836" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C836" s="3" t="n">
@@ -22191,7 +22250,7 @@
       </c>
       <c r="E836" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-36</t>
+          <t>TREMIE-21-36</t>
         </is>
       </c>
       <c r="F836" s="3" t="n">
@@ -22206,7 +22265,7 @@
       </c>
       <c r="B837" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C837" s="5" t="n">
@@ -22217,7 +22276,7 @@
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-37</t>
+          <t>TREMIE-21-37</t>
         </is>
       </c>
       <c r="F837" s="5" t="n">
@@ -22232,7 +22291,7 @@
       </c>
       <c r="B838" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C838" s="3" t="n">
@@ -22243,7 +22302,7 @@
       </c>
       <c r="E838" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-38</t>
+          <t>TREMIE-21-38</t>
         </is>
       </c>
       <c r="F838" s="3" t="n">
@@ -22258,7 +22317,7 @@
       </c>
       <c r="B839" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C839" s="5" t="n">
@@ -22269,7 +22328,7 @@
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-39</t>
+          <t>TREMIE-21-39</t>
         </is>
       </c>
       <c r="F839" s="5" t="n">
@@ -22284,7 +22343,7 @@
       </c>
       <c r="B840" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C840" s="3" t="n">
@@ -22295,7 +22354,7 @@
       </c>
       <c r="E840" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-40</t>
+          <t>TREMIE-21-40</t>
         </is>
       </c>
       <c r="F840" s="3" t="n">
@@ -22310,7 +22369,7 @@
       </c>
       <c r="B841" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C841" s="5" t="n">
@@ -22321,7 +22380,7 @@
       </c>
       <c r="E841" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-41</t>
+          <t>TREMIE-21-41</t>
         </is>
       </c>
       <c r="F841" s="5" t="n">
@@ -22336,7 +22395,7 @@
       </c>
       <c r="B842" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C842" s="3" t="n">
@@ -22347,7 +22406,7 @@
       </c>
       <c r="E842" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-42</t>
+          <t>TREMIE-21-42</t>
         </is>
       </c>
       <c r="F842" s="3" t="n">
@@ -22362,7 +22421,7 @@
       </c>
       <c r="B843" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C843" s="5" t="n">
@@ -22373,7 +22432,7 @@
       </c>
       <c r="E843" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-43</t>
+          <t>TREMIE-21-43</t>
         </is>
       </c>
       <c r="F843" s="5" t="n">
@@ -22388,7 +22447,7 @@
       </c>
       <c r="B844" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C844" s="3" t="n">
@@ -22399,7 +22458,7 @@
       </c>
       <c r="E844" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-44</t>
+          <t>TREMIE-21-44</t>
         </is>
       </c>
       <c r="F844" s="3" t="n">
@@ -22414,7 +22473,7 @@
       </c>
       <c r="B845" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C845" s="5" t="n">
@@ -22425,7 +22484,7 @@
       </c>
       <c r="E845" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-45</t>
+          <t>TREMIE-21-45</t>
         </is>
       </c>
       <c r="F845" s="5" t="n">
@@ -22440,7 +22499,7 @@
       </c>
       <c r="B846" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C846" s="3" t="n">
@@ -22451,7 +22510,7 @@
       </c>
       <c r="E846" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-46</t>
+          <t>TREMIE-21-46</t>
         </is>
       </c>
       <c r="F846" s="3" t="n">
@@ -22466,7 +22525,7 @@
       </c>
       <c r="B847" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C847" s="5" t="n">
@@ -22477,7 +22536,7 @@
       </c>
       <c r="E847" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-47</t>
+          <t>TREMIE-21-47</t>
         </is>
       </c>
       <c r="F847" s="5" t="n">
@@ -22492,7 +22551,7 @@
       </c>
       <c r="B848" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C848" s="3" t="n">
@@ -22503,7 +22562,7 @@
       </c>
       <c r="E848" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-48</t>
+          <t>TREMIE-21-48</t>
         </is>
       </c>
       <c r="F848" s="3" t="n">
@@ -22518,7 +22577,7 @@
       </c>
       <c r="B849" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C849" s="5" t="n">
@@ -22529,7 +22588,7 @@
       </c>
       <c r="E849" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-49</t>
+          <t>TREMIE-21-49</t>
         </is>
       </c>
       <c r="F849" s="5" t="n">
@@ -22544,7 +22603,7 @@
       </c>
       <c r="B850" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C850" s="3" t="n">
@@ -22555,7 +22614,7 @@
       </c>
       <c r="E850" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-50</t>
+          <t>TREMIE-21-50</t>
         </is>
       </c>
       <c r="F850" s="3" t="n">
@@ -22570,7 +22629,7 @@
       </c>
       <c r="B851" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C851" s="5" t="n">
@@ -22581,7 +22640,7 @@
       </c>
       <c r="E851" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-51</t>
+          <t>TREMIE-21-51</t>
         </is>
       </c>
       <c r="F851" s="5" t="n">
@@ -22596,7 +22655,7 @@
       </c>
       <c r="B852" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C852" s="3" t="n">
@@ -22607,7 +22666,7 @@
       </c>
       <c r="E852" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-52</t>
+          <t>TREMIE-21-52</t>
         </is>
       </c>
       <c r="F852" s="3" t="n">
@@ -22622,7 +22681,7 @@
       </c>
       <c r="B853" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C853" s="5" t="n">
@@ -22633,7 +22692,7 @@
       </c>
       <c r="E853" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-53</t>
+          <t>TREMIE-21-53</t>
         </is>
       </c>
       <c r="F853" s="5" t="n">
@@ -22648,7 +22707,7 @@
       </c>
       <c r="B854" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C854" s="3" t="n">
@@ -22659,7 +22718,7 @@
       </c>
       <c r="E854" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-54</t>
+          <t>TREMIE-21-54</t>
         </is>
       </c>
       <c r="F854" s="3" t="n">
@@ -22674,7 +22733,7 @@
       </c>
       <c r="B855" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C855" s="5" t="n">
@@ -22685,7 +22744,7 @@
       </c>
       <c r="E855" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-21-55</t>
+          <t>TREMIE-21-55</t>
         </is>
       </c>
       <c r="F855" s="5" t="n">
@@ -22700,7 +22759,7 @@
       </c>
       <c r="B856" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C856" s="3" t="n">
@@ -22711,7 +22770,7 @@
       </c>
       <c r="E856" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-21-56</t>
+          <t>TREMIE-21-56</t>
         </is>
       </c>
       <c r="F856" s="3" t="n">
@@ -22726,7 +22785,7 @@
       </c>
       <c r="B857" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C857" s="5" t="n">
@@ -22737,7 +22796,7 @@
       </c>
       <c r="E857" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-0</t>
+          <t>TREMIE-28-0</t>
         </is>
       </c>
       <c r="F857" s="5" t="n">
@@ -22752,7 +22811,7 @@
       </c>
       <c r="B858" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C858" s="3" t="n">
@@ -22763,7 +22822,7 @@
       </c>
       <c r="E858" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-1</t>
+          <t>TREMIE-28-1</t>
         </is>
       </c>
       <c r="F858" s="3" t="n">
@@ -22778,7 +22837,7 @@
       </c>
       <c r="B859" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C859" s="5" t="n">
@@ -22789,7 +22848,7 @@
       </c>
       <c r="E859" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-2</t>
+          <t>TREMIE-28-2</t>
         </is>
       </c>
       <c r="F859" s="5" t="n">
@@ -22804,7 +22863,7 @@
       </c>
       <c r="B860" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C860" s="3" t="n">
@@ -22815,7 +22874,7 @@
       </c>
       <c r="E860" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-3</t>
+          <t>TREMIE-28-3</t>
         </is>
       </c>
       <c r="F860" s="3" t="n">
@@ -22830,7 +22889,7 @@
       </c>
       <c r="B861" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C861" s="5" t="n">
@@ -22841,7 +22900,7 @@
       </c>
       <c r="E861" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-4</t>
+          <t>TREMIE-28-4</t>
         </is>
       </c>
       <c r="F861" s="5" t="n">
@@ -22856,7 +22915,7 @@
       </c>
       <c r="B862" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C862" s="3" t="n">
@@ -22867,7 +22926,7 @@
       </c>
       <c r="E862" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-5</t>
+          <t>TREMIE-28-5</t>
         </is>
       </c>
       <c r="F862" s="3" t="n">
@@ -22882,7 +22941,7 @@
       </c>
       <c r="B863" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C863" s="5" t="n">
@@ -22893,7 +22952,7 @@
       </c>
       <c r="E863" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-6</t>
+          <t>TREMIE-28-6</t>
         </is>
       </c>
       <c r="F863" s="5" t="n">
@@ -22908,7 +22967,7 @@
       </c>
       <c r="B864" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C864" s="3" t="n">
@@ -22919,7 +22978,7 @@
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-7</t>
+          <t>TREMIE-28-7</t>
         </is>
       </c>
       <c r="F864" s="3" t="n">
@@ -22934,7 +22993,7 @@
       </c>
       <c r="B865" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C865" s="5" t="n">
@@ -22945,7 +23004,7 @@
       </c>
       <c r="E865" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-8</t>
+          <t>TREMIE-28-8</t>
         </is>
       </c>
       <c r="F865" s="5" t="n">
@@ -22960,7 +23019,7 @@
       </c>
       <c r="B866" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C866" s="3" t="n">
@@ -22971,7 +23030,7 @@
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-9</t>
+          <t>TREMIE-28-9</t>
         </is>
       </c>
       <c r="F866" s="3" t="n">
@@ -22986,7 +23045,7 @@
       </c>
       <c r="B867" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C867" s="5" t="n">
@@ -22997,7 +23056,7 @@
       </c>
       <c r="E867" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-10</t>
+          <t>TREMIE-28-10</t>
         </is>
       </c>
       <c r="F867" s="5" t="n">
@@ -23012,7 +23071,7 @@
       </c>
       <c r="B868" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C868" s="3" t="n">
@@ -23023,7 +23082,7 @@
       </c>
       <c r="E868" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-11</t>
+          <t>TREMIE-28-11</t>
         </is>
       </c>
       <c r="F868" s="3" t="n">
@@ -23038,7 +23097,7 @@
       </c>
       <c r="B869" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C869" s="5" t="n">
@@ -23049,7 +23108,7 @@
       </c>
       <c r="E869" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-12</t>
+          <t>TREMIE-28-12</t>
         </is>
       </c>
       <c r="F869" s="5" t="n">
@@ -23064,7 +23123,7 @@
       </c>
       <c r="B870" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C870" s="3" t="n">
@@ -23075,7 +23134,7 @@
       </c>
       <c r="E870" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-13</t>
+          <t>TREMIE-28-13</t>
         </is>
       </c>
       <c r="F870" s="3" t="n">
@@ -23090,7 +23149,7 @@
       </c>
       <c r="B871" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C871" s="5" t="n">
@@ -23101,7 +23160,7 @@
       </c>
       <c r="E871" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-14</t>
+          <t>TREMIE-28-14</t>
         </is>
       </c>
       <c r="F871" s="5" t="n">
@@ -23116,7 +23175,7 @@
       </c>
       <c r="B872" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C872" s="3" t="n">
@@ -23127,7 +23186,7 @@
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-15</t>
+          <t>TREMIE-28-15</t>
         </is>
       </c>
       <c r="F872" s="3" t="n">
@@ -23142,7 +23201,7 @@
       </c>
       <c r="B873" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C873" s="5" t="n">
@@ -23153,7 +23212,7 @@
       </c>
       <c r="E873" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-16</t>
+          <t>TREMIE-28-16</t>
         </is>
       </c>
       <c r="F873" s="5" t="n">
@@ -23168,7 +23227,7 @@
       </c>
       <c r="B874" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C874" s="3" t="n">
@@ -23179,7 +23238,7 @@
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-17</t>
+          <t>TREMIE-28-17</t>
         </is>
       </c>
       <c r="F874" s="3" t="n">
@@ -23194,7 +23253,7 @@
       </c>
       <c r="B875" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C875" s="5" t="n">
@@ -23205,7 +23264,7 @@
       </c>
       <c r="E875" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-18</t>
+          <t>TREMIE-28-18</t>
         </is>
       </c>
       <c r="F875" s="5" t="n">
@@ -23220,7 +23279,7 @@
       </c>
       <c r="B876" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C876" s="3" t="n">
@@ -23231,7 +23290,7 @@
       </c>
       <c r="E876" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-19</t>
+          <t>TREMIE-28-19</t>
         </is>
       </c>
       <c r="F876" s="3" t="n">
@@ -23246,7 +23305,7 @@
       </c>
       <c r="B877" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C877" s="5" t="n">
@@ -23257,7 +23316,7 @@
       </c>
       <c r="E877" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-20</t>
+          <t>TREMIE-28-20</t>
         </is>
       </c>
       <c r="F877" s="5" t="n">
@@ -23272,7 +23331,7 @@
       </c>
       <c r="B878" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C878" s="3" t="n">
@@ -23283,7 +23342,7 @@
       </c>
       <c r="E878" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-21</t>
+          <t>TREMIE-28-21</t>
         </is>
       </c>
       <c r="F878" s="3" t="n">
@@ -23298,7 +23357,7 @@
       </c>
       <c r="B879" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C879" s="5" t="n">
@@ -23309,7 +23368,7 @@
       </c>
       <c r="E879" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-22</t>
+          <t>TREMIE-28-22</t>
         </is>
       </c>
       <c r="F879" s="5" t="n">
@@ -23324,7 +23383,7 @@
       </c>
       <c r="B880" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C880" s="3" t="n">
@@ -23335,7 +23394,7 @@
       </c>
       <c r="E880" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-23</t>
+          <t>TREMIE-28-23</t>
         </is>
       </c>
       <c r="F880" s="3" t="n">
@@ -23350,7 +23409,7 @@
       </c>
       <c r="B881" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C881" s="5" t="n">
@@ -23361,7 +23420,7 @@
       </c>
       <c r="E881" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-24</t>
+          <t>TREMIE-28-24</t>
         </is>
       </c>
       <c r="F881" s="5" t="n">
@@ -23376,7 +23435,7 @@
       </c>
       <c r="B882" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C882" s="3" t="n">
@@ -23387,7 +23446,7 @@
       </c>
       <c r="E882" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-25</t>
+          <t>TREMIE-28-25</t>
         </is>
       </c>
       <c r="F882" s="3" t="n">
@@ -23402,7 +23461,7 @@
       </c>
       <c r="B883" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C883" s="5" t="n">
@@ -23413,7 +23472,7 @@
       </c>
       <c r="E883" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-26</t>
+          <t>TREMIE-28-26</t>
         </is>
       </c>
       <c r="F883" s="5" t="n">
@@ -23428,7 +23487,7 @@
       </c>
       <c r="B884" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C884" s="3" t="n">
@@ -23439,7 +23498,7 @@
       </c>
       <c r="E884" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-27</t>
+          <t>TREMIE-28-27</t>
         </is>
       </c>
       <c r="F884" s="3" t="n">
@@ -23454,7 +23513,7 @@
       </c>
       <c r="B885" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C885" s="5" t="n">
@@ -23465,7 +23524,7 @@
       </c>
       <c r="E885" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-28</t>
+          <t>TREMIE-28-28</t>
         </is>
       </c>
       <c r="F885" s="5" t="n">
@@ -23480,7 +23539,7 @@
       </c>
       <c r="B886" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C886" s="3" t="n">
@@ -23491,7 +23550,7 @@
       </c>
       <c r="E886" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-29</t>
+          <t>TREMIE-28-29</t>
         </is>
       </c>
       <c r="F886" s="3" t="n">
@@ -23506,7 +23565,7 @@
       </c>
       <c r="B887" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C887" s="5" t="n">
@@ -23517,7 +23576,7 @@
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-30</t>
+          <t>TREMIE-28-30</t>
         </is>
       </c>
       <c r="F887" s="5" t="n">
@@ -23532,7 +23591,7 @@
       </c>
       <c r="B888" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C888" s="3" t="n">
@@ -23543,7 +23602,7 @@
       </c>
       <c r="E888" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-31</t>
+          <t>TREMIE-28-31</t>
         </is>
       </c>
       <c r="F888" s="3" t="n">
@@ -23558,7 +23617,7 @@
       </c>
       <c r="B889" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C889" s="5" t="n">
@@ -23569,7 +23628,7 @@
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-32</t>
+          <t>TREMIE-28-32</t>
         </is>
       </c>
       <c r="F889" s="5" t="n">
@@ -23584,7 +23643,7 @@
       </c>
       <c r="B890" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C890" s="3" t="n">
@@ -23595,7 +23654,7 @@
       </c>
       <c r="E890" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-33</t>
+          <t>TREMIE-28-33</t>
         </is>
       </c>
       <c r="F890" s="3" t="n">
@@ -23610,7 +23669,7 @@
       </c>
       <c r="B891" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C891" s="5" t="n">
@@ -23621,7 +23680,7 @@
       </c>
       <c r="E891" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-34</t>
+          <t>TREMIE-28-34</t>
         </is>
       </c>
       <c r="F891" s="5" t="n">
@@ -23636,7 +23695,7 @@
       </c>
       <c r="B892" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C892" s="3" t="n">
@@ -23647,7 +23706,7 @@
       </c>
       <c r="E892" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-35</t>
+          <t>TREMIE-28-35</t>
         </is>
       </c>
       <c r="F892" s="3" t="n">
@@ -23662,7 +23721,7 @@
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C893" s="5" t="n">
@@ -23673,7 +23732,7 @@
       </c>
       <c r="E893" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-36</t>
+          <t>TREMIE-28-36</t>
         </is>
       </c>
       <c r="F893" s="5" t="n">
@@ -23688,7 +23747,7 @@
       </c>
       <c r="B894" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C894" s="3" t="n">
@@ -23699,7 +23758,7 @@
       </c>
       <c r="E894" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-37</t>
+          <t>TREMIE-28-37</t>
         </is>
       </c>
       <c r="F894" s="3" t="n">
@@ -23714,7 +23773,7 @@
       </c>
       <c r="B895" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C895" s="5" t="n">
@@ -23725,7 +23784,7 @@
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-38</t>
+          <t>TREMIE-28-38</t>
         </is>
       </c>
       <c r="F895" s="5" t="n">
@@ -23740,7 +23799,7 @@
       </c>
       <c r="B896" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C896" s="3" t="n">
@@ -23751,7 +23810,7 @@
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-39</t>
+          <t>TREMIE-28-39</t>
         </is>
       </c>
       <c r="F896" s="3" t="n">
@@ -23766,7 +23825,7 @@
       </c>
       <c r="B897" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C897" s="5" t="n">
@@ -23777,7 +23836,7 @@
       </c>
       <c r="E897" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-40</t>
+          <t>TREMIE-28-40</t>
         </is>
       </c>
       <c r="F897" s="5" t="n">
@@ -23792,7 +23851,7 @@
       </c>
       <c r="B898" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C898" s="3" t="n">
@@ -23803,7 +23862,7 @@
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-41</t>
+          <t>TREMIE-28-41</t>
         </is>
       </c>
       <c r="F898" s="3" t="n">
@@ -23818,7 +23877,7 @@
       </c>
       <c r="B899" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C899" s="5" t="n">
@@ -23829,7 +23888,7 @@
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-42</t>
+          <t>TREMIE-28-42</t>
         </is>
       </c>
       <c r="F899" s="5" t="n">
@@ -23844,7 +23903,7 @@
       </c>
       <c r="B900" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C900" s="3" t="n">
@@ -23855,7 +23914,7 @@
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-43</t>
+          <t>TREMIE-28-43</t>
         </is>
       </c>
       <c r="F900" s="3" t="n">
@@ -23870,7 +23929,7 @@
       </c>
       <c r="B901" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C901" s="5" t="n">
@@ -23881,7 +23940,7 @@
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-44</t>
+          <t>TREMIE-28-44</t>
         </is>
       </c>
       <c r="F901" s="5" t="n">
@@ -23896,7 +23955,7 @@
       </c>
       <c r="B902" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C902" s="3" t="n">
@@ -23907,7 +23966,7 @@
       </c>
       <c r="E902" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-45</t>
+          <t>TREMIE-28-45</t>
         </is>
       </c>
       <c r="F902" s="3" t="n">
@@ -23922,7 +23981,7 @@
       </c>
       <c r="B903" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C903" s="5" t="n">
@@ -23933,7 +23992,7 @@
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-46</t>
+          <t>TREMIE-28-46</t>
         </is>
       </c>
       <c r="F903" s="5" t="n">
@@ -23948,7 +24007,7 @@
       </c>
       <c r="B904" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C904" s="3" t="n">
@@ -23959,7 +24018,7 @@
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-47</t>
+          <t>TREMIE-28-47</t>
         </is>
       </c>
       <c r="F904" s="3" t="n">
@@ -23974,7 +24033,7 @@
       </c>
       <c r="B905" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C905" s="5" t="n">
@@ -23985,7 +24044,7 @@
       </c>
       <c r="E905" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-48</t>
+          <t>TREMIE-28-48</t>
         </is>
       </c>
       <c r="F905" s="5" t="n">
@@ -24000,7 +24059,7 @@
       </c>
       <c r="B906" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C906" s="3" t="n">
@@ -24011,7 +24070,7 @@
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-49</t>
+          <t>TREMIE-28-49</t>
         </is>
       </c>
       <c r="F906" s="3" t="n">
@@ -24026,7 +24085,7 @@
       </c>
       <c r="B907" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C907" s="5" t="n">
@@ -24037,7 +24096,7 @@
       </c>
       <c r="E907" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-50</t>
+          <t>TREMIE-28-50</t>
         </is>
       </c>
       <c r="F907" s="5" t="n">
@@ -24052,7 +24111,7 @@
       </c>
       <c r="B908" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C908" s="3" t="n">
@@ -24063,7 +24122,7 @@
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-51</t>
+          <t>TREMIE-28-51</t>
         </is>
       </c>
       <c r="F908" s="3" t="n">
@@ -24078,7 +24137,7 @@
       </c>
       <c r="B909" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C909" s="5" t="n">
@@ -24089,7 +24148,7 @@
       </c>
       <c r="E909" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-52</t>
+          <t>TREMIE-28-52</t>
         </is>
       </c>
       <c r="F909" s="5" t="n">
@@ -24104,7 +24163,7 @@
       </c>
       <c r="B910" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C910" s="3" t="n">
@@ -24115,7 +24174,7 @@
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-53</t>
+          <t>TREMIE-28-53</t>
         </is>
       </c>
       <c r="F910" s="3" t="n">
@@ -24130,7 +24189,7 @@
       </c>
       <c r="B911" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C911" s="5" t="n">
@@ -24141,7 +24200,7 @@
       </c>
       <c r="E911" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-54</t>
+          <t>TREMIE-28-54</t>
         </is>
       </c>
       <c r="F911" s="5" t="n">
@@ -24156,7 +24215,7 @@
       </c>
       <c r="B912" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C912" s="3" t="n">
@@ -24167,7 +24226,7 @@
       </c>
       <c r="E912" s="3" t="inlineStr">
         <is>
-          <t>Pilotaje-28-55</t>
+          <t>TREMIE-28-55</t>
         </is>
       </c>
       <c r="F912" s="3" t="n">
@@ -24182,7 +24241,7 @@
       </c>
       <c r="B913" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje</t>
+          <t>TREMIE</t>
         </is>
       </c>
       <c r="C913" s="5" t="n">
@@ -24193,7 +24252,7 @@
       </c>
       <c r="E913" s="5" t="inlineStr">
         <is>
-          <t>Pilotaje-28-56</t>
+          <t>TREMIE-28-56</t>
         </is>
       </c>
       <c r="F913" s="5" t="n">
@@ -24202,5 +24261,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>